--- a/artfynd/A 70608-2021 artfynd.xlsx
+++ b/artfynd/A 70608-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124191784</v>
+        <v>124191346</v>
       </c>
       <c r="B2" t="n">
-        <v>103528</v>
+        <v>57666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222412</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,29 +713,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sparrtorp, Sparrtorp, Upl</t>
+          <t>Röby, Röby, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>685365</v>
+        <v>685409</v>
       </c>
       <c r="R2" t="n">
-        <v>6619336</v>
+        <v>6619234</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -791,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124191346</v>
+        <v>124191784</v>
       </c>
       <c r="B3" t="n">
-        <v>57666</v>
+        <v>103528</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>222412</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -829,24 +824,29 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Röby, Röby, Upl</t>
+          <t>Sparrtorp, Sparrtorp, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>685409</v>
+        <v>685365</v>
       </c>
       <c r="R3" t="n">
-        <v>6619234</v>
+        <v>6619336</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>

--- a/artfynd/A 70608-2021 artfynd.xlsx
+++ b/artfynd/A 70608-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124191346</v>
+        <v>124191784</v>
       </c>
       <c r="B2" t="n">
-        <v>57666</v>
+        <v>103528</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>222412</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,24 +713,29 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Röby, Röby, Upl</t>
+          <t>Sparrtorp, Sparrtorp, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>685409</v>
+        <v>685365</v>
       </c>
       <c r="R2" t="n">
-        <v>6619234</v>
+        <v>6619336</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -786,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124191784</v>
+        <v>124191346</v>
       </c>
       <c r="B3" t="n">
-        <v>103528</v>
+        <v>57666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +803,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222412</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -824,29 +829,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sparrtorp, Sparrtorp, Upl</t>
+          <t>Röby, Röby, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>685365</v>
+        <v>685409</v>
       </c>
       <c r="R3" t="n">
-        <v>6619336</v>
+        <v>6619234</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>

--- a/artfynd/A 70608-2021 artfynd.xlsx
+++ b/artfynd/A 70608-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>124191346</v>
       </c>
       <c r="B2" t="n">
-        <v>57666</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,12 +784,7 @@
         <v>124191784</v>
       </c>
       <c r="B3" t="n">
-        <v>103528</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104628</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,6 +889,117 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>124192252</v>
+      </c>
+      <c r="B4" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Sparrtorp, Sparrtorp, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>685239</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6619303</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 70608-2021 artfynd.xlsx
+++ b/artfynd/A 70608-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1018,6 +1018,780 @@
       <c r="AZ4" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/124192252</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135930131</v>
+      </c>
+      <c r="B5" t="n">
+        <v>92050</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Röbykärret, Röbykärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>685628</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6618968</v>
+      </c>
+      <c r="S5" t="n">
+        <v>15</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Kalle Skarin</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Kalle Skarin</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135930131</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135928572</v>
+      </c>
+      <c r="B6" t="n">
+        <v>96861</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Röbykärret, Röbykärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>685546</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6619044</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Utspridd blåmussla över hällen. Storlekar om 2x3 dm utspridda över ett område på 15 kvm</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Nadine Rosenhall Gomis</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Nadine Rosenhall Gomis</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135928572</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135929366</v>
+      </c>
+      <c r="B7" t="n">
+        <v>96861</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Sparrtorp, Sparrtorp, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>685567</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6619023</v>
+      </c>
+      <c r="S7" t="n">
+        <v>20</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jakob Nygren</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jakob Nygren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135929366</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135929588</v>
+      </c>
+      <c r="B8" t="n">
+        <v>96861</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Röbykärret, Röbykärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>685602</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6618990</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Mellan gamla hjulspår  i fuktigare kanske sumpblandskog</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Nadine Rosenhall Gomis</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Nadine Rosenhall Gomis</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135929588</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135932783</v>
+      </c>
+      <c r="B9" t="n">
+        <v>5181</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ryttartorp, Ryttartorp, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>685587</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6619180</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Kalle Skarin</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Kalle Skarin</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135932783</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135932821</v>
+      </c>
+      <c r="B10" t="n">
+        <v>5201</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ryttartorp, Ryttartorp, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>685588</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6619188</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Kalle Skarin</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Kalle Skarin</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135932821</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135928047</v>
+      </c>
+      <c r="B11" t="n">
+        <v>8461</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Ryttartorp, Ryttartorp, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>685557</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6619147</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Nadine Rosenhall Gomis</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Nadine Rosenhall Gomis</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135928047</t>
         </is>
       </c>
     </row>
@@ -1026,6 +1800,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 70608-2021 artfynd.xlsx
+++ b/artfynd/A 70608-2021 artfynd.xlsx
@@ -1026,7 +1026,7 @@
         <v>135930131</v>
       </c>
       <c r="B5" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>135928572</v>
       </c>
       <c r="B6" t="n">
-        <v>96861</v>
+        <v>96878</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>135929366</v>
       </c>
       <c r="B7" t="n">
-        <v>96861</v>
+        <v>96878</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>135929588</v>
       </c>
       <c r="B8" t="n">
-        <v>96861</v>
+        <v>96878</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>135932783</v>
       </c>
       <c r="B9" t="n">
-        <v>5181</v>
+        <v>5182</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>135932821</v>
       </c>
       <c r="B10" t="n">
-        <v>5201</v>
+        <v>5202</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         <v>135928047</v>
       </c>
       <c r="B11" t="n">
-        <v>8461</v>
+        <v>8463</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 70608-2021 artfynd.xlsx
+++ b/artfynd/A 70608-2021 artfynd.xlsx
@@ -1026,7 +1026,7 @@
         <v>135930131</v>
       </c>
       <c r="B5" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>135928572</v>
       </c>
       <c r="B6" t="n">
-        <v>96878</v>
+        <v>96879</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>135929366</v>
       </c>
       <c r="B7" t="n">
-        <v>96878</v>
+        <v>96879</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>135929588</v>
       </c>
       <c r="B8" t="n">
-        <v>96878</v>
+        <v>96879</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 70608-2021 artfynd.xlsx
+++ b/artfynd/A 70608-2021 artfynd.xlsx
@@ -1026,7 +1026,7 @@
         <v>135930131</v>
       </c>
       <c r="B5" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>135928572</v>
       </c>
       <c r="B6" t="n">
-        <v>96879</v>
+        <v>96880</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>135929366</v>
       </c>
       <c r="B7" t="n">
-        <v>96879</v>
+        <v>96880</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>135929588</v>
       </c>
       <c r="B8" t="n">
-        <v>96879</v>
+        <v>96880</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 70608-2021 artfynd.xlsx
+++ b/artfynd/A 70608-2021 artfynd.xlsx
@@ -1026,7 +1026,7 @@
         <v>135930131</v>
       </c>
       <c r="B5" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>135928572</v>
       </c>
       <c r="B6" t="n">
-        <v>96880</v>
+        <v>96881</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>135929366</v>
       </c>
       <c r="B7" t="n">
-        <v>96880</v>
+        <v>96881</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>135929588</v>
       </c>
       <c r="B8" t="n">
-        <v>96880</v>
+        <v>96881</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 70608-2021 artfynd.xlsx
+++ b/artfynd/A 70608-2021 artfynd.xlsx
@@ -1026,7 +1026,7 @@
         <v>135930131</v>
       </c>
       <c r="B5" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>135928572</v>
       </c>
       <c r="B6" t="n">
-        <v>96881</v>
+        <v>96887</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>135929366</v>
       </c>
       <c r="B7" t="n">
-        <v>96881</v>
+        <v>96887</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>135929588</v>
       </c>
       <c r="B8" t="n">
-        <v>96881</v>
+        <v>96887</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 70608-2021 artfynd.xlsx
+++ b/artfynd/A 70608-2021 artfynd.xlsx
@@ -1026,7 +1026,7 @@
         <v>135930131</v>
       </c>
       <c r="B5" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>135928572</v>
       </c>
       <c r="B6" t="n">
-        <v>96887</v>
+        <v>96888</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>135929366</v>
       </c>
       <c r="B7" t="n">
-        <v>96887</v>
+        <v>96888</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>135929588</v>
       </c>
       <c r="B8" t="n">
-        <v>96887</v>
+        <v>96888</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 70608-2021 artfynd.xlsx
+++ b/artfynd/A 70608-2021 artfynd.xlsx
@@ -1026,7 +1026,7 @@
         <v>135930131</v>
       </c>
       <c r="B5" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>135928572</v>
       </c>
       <c r="B6" t="n">
-        <v>96888</v>
+        <v>96899</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>135929366</v>
       </c>
       <c r="B7" t="n">
-        <v>96888</v>
+        <v>96899</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>135929588</v>
       </c>
       <c r="B8" t="n">
-        <v>96888</v>
+        <v>96899</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 70608-2021 artfynd.xlsx
+++ b/artfynd/A 70608-2021 artfynd.xlsx
@@ -1026,7 +1026,7 @@
         <v>135930131</v>
       </c>
       <c r="B5" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>135928572</v>
       </c>
       <c r="B6" t="n">
-        <v>96899</v>
+        <v>96912</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>135929366</v>
       </c>
       <c r="B7" t="n">
-        <v>96899</v>
+        <v>96912</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>135929588</v>
       </c>
       <c r="B8" t="n">
-        <v>96899</v>
+        <v>96912</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 70608-2021 artfynd.xlsx
+++ b/artfynd/A 70608-2021 artfynd.xlsx
@@ -1026,7 +1026,7 @@
         <v>135930131</v>
       </c>
       <c r="B5" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>135928572</v>
       </c>
       <c r="B6" t="n">
-        <v>96912</v>
+        <v>96913</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>135929366</v>
       </c>
       <c r="B7" t="n">
-        <v>96912</v>
+        <v>96913</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>135929588</v>
       </c>
       <c r="B8" t="n">
-        <v>96912</v>
+        <v>96913</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 70608-2021 artfynd.xlsx
+++ b/artfynd/A 70608-2021 artfynd.xlsx
@@ -1026,7 +1026,7 @@
         <v>135930131</v>
       </c>
       <c r="B5" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>135928572</v>
       </c>
       <c r="B6" t="n">
-        <v>96913</v>
+        <v>96926</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>135929366</v>
       </c>
       <c r="B7" t="n">
-        <v>96913</v>
+        <v>96926</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>135929588</v>
       </c>
       <c r="B8" t="n">
-        <v>96913</v>
+        <v>96926</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 70608-2021 artfynd.xlsx
+++ b/artfynd/A 70608-2021 artfynd.xlsx
@@ -1026,7 +1026,7 @@
         <v>135930131</v>
       </c>
       <c r="B5" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>135928572</v>
       </c>
       <c r="B6" t="n">
-        <v>96926</v>
+        <v>96927</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>135929366</v>
       </c>
       <c r="B7" t="n">
-        <v>96926</v>
+        <v>96927</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>135929588</v>
       </c>
       <c r="B8" t="n">
-        <v>96926</v>
+        <v>96927</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
